--- a/code/Book1.xlsx
+++ b/code/Book1.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27830"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Rahamatha\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\sample\code\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8992E41A-3626-4978-B915-811DB8EC41F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F47C69DD-C8BE-4ED2-A031-83C8B99195B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{B3A9D0ED-BEC4-40F4-80EC-771A2CC96041}"/>
   </bookViews>
@@ -34,12 +34,24 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
   <si>
     <t>[10:02 am, 12/08/2024] Jayasri Sri: https://drive.google.com/drive/folders/1fEsfQr-6U5YHciLJ976xa0Ooy1LovBCD?usp=sharing</t>
   </si>
   <si>
     <t>[10:07 am, 12/08/2024] Jayasri Sri: https://youtu.be/QxA-7VLT74k?si=-LjufLIzGNjQrof1</t>
+  </si>
+  <si>
+    <t>rahamatunnisa</t>
+  </si>
+  <si>
+    <t>thushkurunnisa</t>
+  </si>
+  <si>
+    <t>bujji</t>
+  </si>
+  <si>
+    <t>mallika</t>
   </si>
 </sst>
 </file>
@@ -391,7 +403,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A8097FE9-04BC-4DF4-93EB-802E9449DFDA}">
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A9"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
@@ -404,6 +416,26 @@
         <v>1</v>
       </c>
     </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
